--- a/reports/一级子公司A_利润表_2025-06.xlsx
+++ b/reports/一级子公司A_利润表_2025-06.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>176501045</v>
+        <v>180590540</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>171978995</v>
+        <v>172191728</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>971471791</v>
+        <v>970317950</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>701213</v>
+        <v>699874</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3954394</v>
+        <v>3962601</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>607733</v>
+        <v>605993</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>3430793</v>
+        <v>3438151</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>517544</v>
+        <v>512742</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2907852</v>
+        <v>2913065</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>474386</v>
+        <v>471329</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2675858</v>
+        <v>2678975</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>259020</v>
+        <v>256178</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1454778</v>
+        <v>1455198</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>206176</v>
+        <v>205146</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1164267</v>
+        <v>1163529</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>173734973</v>
+        <v>177839278</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>169212923</v>
+        <v>169440466</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>86887968</v>
+        <v>87047073</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>492470963</v>
+        <v>491123702</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1592177</v>
+        <v>1601523</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>9030625</v>
+        <v>9009271</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1435321</v>
+        <v>1449216</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>8152650</v>
+        <v>8141384</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>77596413</v>
+        <v>77614990</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>436519992</v>
+        <v>436677598</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1638603</v>
+        <v>1653840</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>9311666</v>
+        <v>9318063</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>722239</v>
+        <v>722734</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4072785</v>
+        <v>4077560</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2562724</v>
+        <v>2572324</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>14546803</v>
+        <v>14569442</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1135727</v>
+        <v>1131551</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>6396932</v>
+        <v>6410201</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4431767</v>
+        <v>4415234</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>25005444</v>
+        <v>25057131</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>90283</v>
+        <v>89582</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>539612</v>
+        <v>540564</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2336038</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>13276120</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1557958</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>8846043</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>118004124</v>
+        <v>126162387</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>105471252</v>
+        <v>105216545</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>103316178</v>
+        <v>103048513</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>582406971</v>
+        <v>581276748</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2155074</v>
+        <v>2168032</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>12232307</v>
+        <v>12206300</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3930502</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>22092079</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1258919</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>7072167</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>786839</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>4422338</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>943372</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>5309666</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>706374</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3984156</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>469929</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2656991</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>390748</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2214448</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1810851</v>
+        <v>1795975</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>10177586</v>
+        <v>10197057</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1390261</v>
+        <v>1383740</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>7852342</v>
+        <v>7863889</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1139325</v>
+        <v>1127026</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>6399576</v>
+        <v>6404875</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8560640</v>
+        <v>8507937</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>48304565</v>
+        <v>48301631</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>351212</v>
+        <v>359194</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2100249</v>
+        <v>2035829</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>670844</v>
+        <v>669027</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>4021709</v>
+        <v>4016705</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>759324</v>
+        <v>669027</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4562720</v>
+        <v>4016705</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>90026</v>
+        <v>90240</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>540418</v>
+        <v>539348</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>343500</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>2049753</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>688510</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3867832</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>229161</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1367532</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>171700</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1026166</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>285676</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1711093</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>978728</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>5535562</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>151705</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>913088</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>113568</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>684798</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>189059</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1141074</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>132301</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>798438</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>94560</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>570033</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>75758</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>455798</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>56932</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>341705</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>55730849</v>
+        <v>54065813</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>64596767</v>
+        <v>60505108</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>393178</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2209396</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>95497</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>569579</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>149714</v>
+        <v>150753</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>900260</v>
+        <v>899742</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>55581135</v>
+        <v>54308238</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5304769</v>
+        <v>5311202</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>31789827</v>
+        <v>31822074</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>50276366</v>
+        <v>48997036</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>50276366</v>
+        <v>48997036</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>50276366</v>
+        <v>48997036</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>50276366</v>
+        <v>48997036</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>50276366</v>
+        <v>48997036</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
